--- a/smeta/Smeta_karkasnyi_dom_posutochno.xlsx
+++ b/smeta/Smeta_karkasnyi_dom_posutochno.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -652,7 +652,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ТОЛЬКО ВНУТРЕННИЕ работы/материалы. Уже есть и НЕ включено: окна, витражи, терраса, наружный контур, кровля, фасад. Внутри — каркас перегородок. Отопление: электрические конвекторы. В смете — ТОЛЬКО материалы и комплектация (без стоимости работ). «Время монтажа» — ориентир, бригада 2 чел. Цены — средние розничные РФ, 2026 г.</t>
+          <t>Отделка стен и потолков — ВАГОНКА (штиль) белая, как на фото; ГКЛ НЕ используется. Уже есть и НЕ включено: окна, витражи, настил террасы, наружный контур, кровля, фасад. Внутри — каркас перегородок. Отопление: электрические конвекторы. Уличная подсветка — включена. В смете — ТОЛЬКО материалы и комплектация (без стоимости работ). «Время монтажа» — ориентир, бригада 2 чел. Цены — средние розничные РФ, 2026 г.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1. ОТДЕЛКА ПЕРЕГОРОДОК И СТЕН ИЗНУТРИ (каркас уже есть)</t>
+          <t>1. ОТДЕЛКА СТЕН ВАГОНКОЙ (как на фото, без ГКЛ)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -757,7 +757,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Пароизоляция / мембрана для перегородок</t>
+          <t>Пароизоляция / мембрана</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -783,35 +783,35 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Гипсокартон ГКЛ 12,5 мм (стены сухие)</t>
+          <t>Брусок обрешётки 40×40 / 20×40 под вагонку (стены)</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>30400</v>
+        <v>7700</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>обе стороны перегородок + внутр. сторона наружных стен</t>
+          <t>шаг ~400–600 мм</t>
         </is>
       </c>
     </row>
@@ -821,11 +821,11 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Гипсокартон ГКЛВ 12,5 мм влагостойкий (с/у)</t>
+          <t>Вагонка штиль хвоя 12–14 мм (стены сухие)</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -833,17 +833,17 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>420</v>
+        <v>650</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>11760</v>
+        <v>84500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>стены санузла</t>
+          <t>≈142.2 м² + запас; горизонтально как на фото</t>
         </is>
       </c>
     </row>
@@ -853,29 +853,29 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Профиль/брусок доборный, саморезы, лента, уголки</t>
+          <t>Вагонка ПВХ / панели влагостойкие (стены с/у, вне мокрой зоны плитки)</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>12000</v>
+        <v>550</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>12000</v>
+        <v>4400</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>крепёж к существующему каркасу</t>
+          <t>если часть стен с/у не под плиткой</t>
         </is>
       </c>
     </row>
@@ -885,31 +885,27 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Серпянка, шпаклёвка стартовая + финишная</t>
+          <t>Саморезы, кляймеры, крепёж для вагонки</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>180</v>
+        <v>8000</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>23400</v>
+        <v>8000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>стены под покраску</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -917,7 +913,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Грунт глубокого проникновения</t>
+          <t>Грунт / антисептик по дереву</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -929,27 +925,27 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>4550</v>
+        <v>7800</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Краска интерьерная моющаяся (2 слоя)</t>
+          <t>Краска / масло-воск укрывистое белое по вагонке (2 слоя)</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
@@ -957,17 +953,17 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>26400</v>
+        <v>36400</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1.5</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>гостиная, спальни, прихожая</t>
+          <t>цвет как на фото — белый</t>
         </is>
       </c>
     </row>
@@ -977,11 +973,11 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Уголки защитные ПВХ на внешние углы</t>
+          <t>Уголки / раскладки деревянные на углы и стыки</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -989,27 +985,27 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2700</v>
+        <v>4800</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Откосы внутренние на окна (сэндвич/ГКЛ+уголок)</t>
+          <t>Наличники / доборы деревянные белые к проёмам</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
@@ -1017,115 +1013,115 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>450</v>
+        <v>280</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>8100</v>
+        <v>8400</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>окна уже стоят — только внутр. отделка откосов</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
+          <t>в тон вагонке</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Подоконники ПВХ белые</t>
+          <t>Откосы внутренние на окна (вагонка / сэндвич белый)</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>450</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>8100</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>окна уже стоят</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Подоконники ПВХ / дерево белые</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>м.п.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>1200</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F18" s="9" t="n">
         <v>7200</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G18" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>если ещё не установлены</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ОТДЕЛКА ПЕРЕГОРОДОК И СТЕН ИЗНУТРИ (каркас уже есть)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="13" t="n">
-        <v>134920</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H18" s="15" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2. ПОТОЛКИ</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Гипсокартон потолочный ГКЛ 9,5–12,5 мм</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>14400</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>43.36 м² + запас</t>
-        </is>
-      </c>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ОТДЕЛКА СТЕН ВАГОНКОЙ (как на фото, без ГКЛ)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="13" t="n">
+        <v>185710</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H19" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2. ПОТОЛКИ ВАГОНКОЙ (как на фото, без ГКЛ)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="n">
@@ -1133,31 +1129,27 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Профиль потолочный CD/UD + подвесы</t>
+          <t>Брусок / рейка обрешётки потолка</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>12000</v>
+        <v>4400</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>каркас потолка</t>
-        </is>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1165,7 +1157,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Шпаклёвка + грунт потолка</t>
+          <t>Вагонка штиль хвоя 12–14 мм на потолок</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -1177,15 +1169,19 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>7200</v>
+        <v>31200</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>43.36 м² + запас</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="6" t="n">
@@ -1193,135 +1189,135 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Краска потолочная белая (2 слоя)</t>
+          <t>Кляймеры / саморезы потолок</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>160</v>
+        <v>3500</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>7680</v>
+        <v>3500</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>16</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Плинтус потолочный / галтель</t>
+          <t>Грунт + краска/масло белое по потолку (2 слоя)</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>13440</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>в тон стенам</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Галтель / плинтус потолочный деревянный</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>м.п.</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E26" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F26" s="9" t="n">
         <v>7200</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G26" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>периметр помещений</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ПОТОЛКИ</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="13" t="n">
-        <v>48480</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H26" s="15" t="inlineStr"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ПОТОЛКИ ВАГОНКОЙ (как на фото, без ГКЛ)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="13" t="n">
+        <v>59740</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H27" s="15" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>3. ПОЛЫ</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Фанера / ОСБ-3 18–21 мм выравнивающая (при необходимости)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>650</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>31200</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>уточнить по существующему черновому полу</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Подложка под ламинат 3 мм</t>
+          <t>Фанера / ОСБ-3 18–21 мм выравнивающая (при необходимости)</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -1329,31 +1325,31 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>3200</v>
+        <v>31200</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>без с/у</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
+          <t>уточнить по существующему черновому полу</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Ламинат 33 кл. влагостойкий (жилые + прихожая)</t>
+          <t>Подложка под ламинат 3 мм</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
@@ -1361,47 +1357,51 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1200</v>
+        <v>80</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>52800</v>
+        <v>3200</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>~40.04 м² + запас 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
+          <t>без с/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Плинтус МДФ/ПВХ с кабель-каналом + уголки</t>
+          <t>Ламинат 33 кл. влагостойкий (жилые + прихожая)</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>220</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>9900</v>
+        <v>52800</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>~40.04 м² + запас 10%</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -1409,25 +1409,25 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Порог / переход алюминиевый</t>
+          <t>Плинтус МДФ/ПВХ с кабель-каналом + уголки</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1800</v>
+        <v>9900</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Наливной пол тонкий в с/у</t>
+          <t>Порог / переход алюминиевый</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
@@ -1455,13 +1455,9 @@
         <v>1800</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>под плитку</t>
-        </is>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -1469,11 +1465,11 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Гидроизоляция обмазочная пола с/у</t>
+          <t>Наливной пол тонкий в с/у</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
@@ -1481,79 +1477,83 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>под плитку</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Гидроизоляция обмазочная пола с/у</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>350</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
           <t>пол + заход на стены 150 мм</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Итого: ПОЛЫ</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="13" t="n">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n">
         <v>103500</v>
       </c>
-      <c r="G36" s="14" t="n">
+      <c r="G37" s="14" t="n">
         <v>4.4</v>
       </c>
-      <c r="H36" s="15" t="inlineStr"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>4. САНУЗЕЛ — плитка и гидроизоляция стен</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Гидроизоляция стен с/у</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>320</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>5760</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="n">
@@ -1561,11 +1561,11 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Плитка настенная 30×60</t>
+          <t>Гидроизоляция стен с/у</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
@@ -1573,19 +1573,15 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>1100</v>
+        <v>320</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>22000</v>
+        <v>5760</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>стены с/у + запас</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -1593,11 +1589,11 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Керамогранит на пол 60×60</t>
+          <t>Плитка настенная 30×60</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
@@ -1605,17 +1601,17 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>5600</v>
+        <v>22000</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>с/у 3.32 м² + запас</t>
+          <t>стены с/у + запас</t>
         </is>
       </c>
     </row>
@@ -1625,27 +1621,31 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Клей + затирка + крестики + уголки</t>
+          <t>Керамогранит на пол 60×60</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6500</v>
+        <v>1400</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>6500</v>
+        <v>5600</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>с/у 3.32 м² + запас</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -1653,99 +1653,95 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
+          <t>Клей + затирка + крестики + уголки</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
           <t>Ревизионный люк</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="n">
+      <c r="C44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>2500</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F44" s="9" t="n">
         <v>2500</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G44" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="H43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Итого: САНУЗЕЛ — плитка и гидроизоляция стен</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="13" t="n">
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="13" t="n">
         <v>42360</v>
       </c>
-      <c r="G44" s="14" t="n">
+      <c r="G45" s="14" t="n">
         <v>2.7</v>
       </c>
-      <c r="H44" s="15" t="inlineStr"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="H45" s="15" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>5. ДВЕРИ МЕЖКОМНАТНЫЕ</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Дверь экошпон + коробка + наличники (ДВ-1 с/у)</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G47" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>влагостойкая, ~700 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Дверь экошпон (ДВ-2 спальня 1)</t>
+          <t>Дверь экошпон + коробка + наличники (ДВ-1 с/у)</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -1757,17 +1753,17 @@
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>проём ~800</t>
+          <t>влагостойкая, ~700 мм</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1773,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Дверь экошпон (ДВ-3 спальня 2)</t>
+          <t>Дверь экошпон (ДВ-2 спальня 1)</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -1809,95 +1805,95 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t>Дверь экошпон (ДВ-3 спальня 2)</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>проём ~800</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>Ручки + защёлки/замки на 3 двери</t>
         </is>
       </c>
-      <c r="C50" s="8" t="n">
+      <c r="C51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E51" s="9" t="n">
         <v>1800</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F51" s="9" t="n">
         <v>5400</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G51" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>замок на с/у</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Итого: ДВЕРИ МЕЖКОМНАТНЫЕ</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="13" t="n">
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="13" t="n">
         <v>39400</v>
       </c>
-      <c r="G51" s="14" t="n">
+      <c r="G52" s="14" t="n">
         <v>1.1</v>
       </c>
-      <c r="H51" s="15" t="inlineStr"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="H52" s="15" t="inlineStr"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>6. ЭЛЕКТРИКА ВНУТРЕННЯЯ (материалы)</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Кабель ВВГнг-LS 3×2,5 (розетки + конвекторы)</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="F54" s="9" t="n">
-        <v>13300</v>
-      </c>
-      <c r="G54" s="10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>отдельные линии на конвекторы</t>
-        </is>
-      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -1905,11 +1901,11 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг-LS 3×1,5 (освещение)</t>
+          <t>Кабель ВВГнг-LS 3×2,5 (розетки + конвекторы)</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
@@ -1917,15 +1913,19 @@
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>7000</v>
+        <v>13300</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>отдельные линии на конвекторы</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="n">
@@ -1933,11 +1933,11 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг-LS 3×6 (ввод / плита)</t>
+          <t>Кабель ВВГнг-LS 3×1,5 (освещение)</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>4400</v>
+        <v>7000</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H56" s="7" t="inlineStr"/>
     </row>
@@ -1961,35 +1961,35 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Гофра / клипсы / кабель-канал</t>
+          <t>Кабель ВВГнг-LS 3×6 (ввод / плита)</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>4500</v>
+        <v>220</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
     </row>
-    <row r="58" ht="32" customHeight="1">
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="n">
         <v>37</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Щит + автоматы + УЗО/диф. (с линиями на конвекторы)</t>
+          <t>Гофра / клипсы / кабель-канал</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -2001,49 +2001,45 @@
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>22000</v>
+        <v>4500</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>22000</v>
+        <v>4500</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>отдельный автомат на каждый конвектор</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="6" t="n">
         <v>38</v>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Розетки + выключатели</t>
+          <t>Щит + автоматы + УЗО/диф. (с линиями на конвекторы)</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>280</v>
+        <v>22000</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>10640</v>
+        <v>22000</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>в т.ч. силовые под конвекторы</t>
+          <t>отдельный автомат на каждый конвектор</t>
         </is>
       </c>
     </row>
@@ -2053,11 +2049,11 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Подрозетники / распредкоробки</t>
+          <t>Розетки + выключатели</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
@@ -2065,15 +2061,19 @@
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>45</v>
+        <v>280</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>2250</v>
+        <v>10640</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>в т.ч. силовые под конвекторы</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Светильники потолочные LED</t>
+          <t>Подрозетники / распредкоробки</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
@@ -2093,19 +2093,15 @@
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>2200</v>
+        <v>45</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>17600</v>
+        <v>2250</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>гостиная, спальни, прихожая</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="6" t="n">
@@ -2113,27 +2109,31 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Подсветка LED кухня + БП</t>
+          <t>Светильники потолочные LED</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>4500</v>
+        <v>2200</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>4500</v>
+        <v>17600</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H62" s="7" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>гостиная, спальни, прихожая</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -2141,25 +2141,25 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Светильник IP44 (с/у)</t>
+          <t>Подсветка LED кухня + БП</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>1800</v>
+        <v>4500</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H63" s="7" t="inlineStr"/>
     </row>
@@ -2169,25 +2169,25 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Тёплый пол электрический мат в с/у</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="n">
-        <v>3.5</v>
+          <t>Светильник IP44 (с/у)</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
         <v>1800</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>6300</v>
+        <v>3600</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H64" s="7" t="inlineStr"/>
     </row>
@@ -2197,35 +2197,35 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Терморегулятор тёплого пола</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n">
-        <v>1</v>
+          <t>Тёплый пол электрический мат в с/у</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>3.5</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>3500</v>
+        <v>1800</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>3500</v>
+        <v>6300</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H65" s="7" t="inlineStr"/>
     </row>
-    <row r="66" ht="32" customHeight="1">
+    <row r="66" ht="20" customHeight="1">
       <c r="A66" s="6" t="n">
         <v>45</v>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Умный замок / электронный на вход (внутр. установка)</t>
+          <t>Терморегулятор тёплого пола</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -2237,27 +2237,23 @@
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>15000</v>
+        <v>3500</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>коды для гостей</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
+        <v>0.1</v>
+      </c>
+      <c r="H66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
       <c r="A67" s="6" t="n">
         <v>46</v>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Звонок / видеодомофон простой</t>
+          <t>Умный замок / электронный на вход (внутр. установка)</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -2265,59 +2261,123 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="G67" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="H67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ЭЛЕКТРИКА ВНУТРЕННЯЯ (материалы)</t>
-        </is>
-      </c>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="13" t="n">
-        <v>122590</v>
-      </c>
-      <c r="G68" s="14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H68" s="15" t="inlineStr"/>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>7. ОТОПЛЕНИЕ — ЭЛЕКТРИЧЕСКИЕ КОНВЕКТОРЫ</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-    </row>
-    <row r="71" ht="32" customHeight="1">
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>коды для гостей</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Звонок / видеодомофон простой</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Кабель ВВГнг-LS 3×1,5 наружный / в гофре на уличное освещение</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>вывод на террасу/фасад</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Светильник уличный LED настенный IP65 (терраса / вход)</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>подсветка террасы и входа</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
       <c r="A71" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Конвектор электрический 2,0 кВт с термостатом (кухня-гостиная)</t>
+          <t>Прожектор / грунтовый светильник LED уличный</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -2329,27 +2389,27 @@
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>9500</v>
+        <v>2800</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>19000</v>
+        <v>5600</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>комната 18.82 м² — 2 шт. по периметру</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="32" customHeight="1">
+          <t>подсветка участка / фасада</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
       <c r="A72" s="6" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Конвектор электрический 1,5 кВт с термостатом (спальня 1)</t>
+          <t>Датчик движения / сумеречное реле для улицы</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -2361,27 +2421,27 @@
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>7500</v>
+        <v>1800</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>7500</v>
+        <v>1800</v>
       </c>
       <c r="G72" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>9.21 м²</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="32" customHeight="1">
+          <t>автоматическое включение</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
       <c r="A73" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Конвектор электрический 1,5 кВт с термостатом (спальня 2)</t>
+          <t>Выключатель уличного света (внутри у двери)</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -2393,107 +2453,47 @@
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>7500</v>
+        <v>350</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>7500</v>
+        <v>350</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>9.21 м²</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Конвектор электрический 1,0 кВт (прихожая / запас)</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>2.8 м²</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Кронштейны / ножки настенного монтажа (в комплекте или добор)</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="n">
-        <v>800</v>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G75" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Полотенцесушитель электрический в с/у</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>6500</v>
-      </c>
-      <c r="G76" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H76" s="7" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="H73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ЭЛЕКТРИКА ВНУТРЕННЯЯ (материалы)</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n"/>
+      <c r="C74" s="12" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="13" t="n">
+        <v>144440</v>
+      </c>
+      <c r="G74" s="14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H74" s="15" t="inlineStr"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>7. ОТОПЛЕНИЕ — ЭЛЕКТРИЧЕСКИЕ КОНВЕКТОРЫ</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
     </row>
     <row r="77" ht="32" customHeight="1">
       <c r="A77" s="6" t="n">
@@ -2501,11 +2501,11 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Программатор / Wi-Fi модуль для конвекторов (опция)</t>
+          <t>Конвектор электрический 2,0 кВт с термостатом (кухня-гостиная)</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
@@ -2513,91 +2513,155 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>3500</v>
+        <v>9500</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>10500</v>
+        <v>19000</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>удобно для посуточной — прогрев перед заездом</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ОТОПЛЕНИЕ — ЭЛЕКТРИЧЕСКИЕ КОНВЕКТОРЫ</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="n"/>
-      <c r="C78" s="12" t="n"/>
-      <c r="D78" s="12" t="n"/>
-      <c r="E78" s="12" t="n"/>
-      <c r="F78" s="13" t="n">
-        <v>61000</v>
-      </c>
-      <c r="G78" s="14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H78" s="15" t="inlineStr"/>
-    </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>8. ВЕНТИЛЯЦИЯ И ВОДОСНАБЖЕНИЕ (внутренняя разводка)</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-    </row>
-    <row r="81" ht="20" customHeight="1">
+          <t>комната 18.82 м² — 2 шт. по периметру</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Конвектор электрический 1,5 кВт с термостатом (спальня 1)</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>9.21 м²</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Конвектор электрический 1,5 кВт с термостатом (спальня 2)</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>9.21 м²</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Конвектор электрический 1,0 кВт (прихожая / запас)</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>2.8 м²</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
       <c r="A81" s="6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Вентилятор вытяжной с/у + обратный клапан</t>
+          <t>Кронштейны / ножки настенного монтажа (в комплекте или добор)</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>2800</v>
+        <v>800</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H81" s="7" t="inlineStr"/>
     </row>
-    <row r="82" ht="32" customHeight="1">
+    <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Приточный клапан стеновой (если нет проветривания окнами)</t>
+          <t>Полотенцесушитель электрический в с/у</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
@@ -2605,139 +2669,79 @@
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>2500</v>
+        <v>6500</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="G82" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Программатор / Wi-Fi модуль для конвекторов (опция)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>10500</v>
+      </c>
+      <c r="G83" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>опция; окна уже есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Труба ППР/металлопласт + фитинги (ХВС/ГВС)</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G83" s="10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>внутренняя разводка до точек</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Канализация ПВХ 50/110 + фитинги</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F84" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Водонагреватель накопительный 50–80 л</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F85" s="9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G85" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>если нет ГВС</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Фильтр грубой очистки + редуктор</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F86" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G86" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H86" s="7" t="inlineStr"/>
+          <t>удобно для посуточной — прогрев перед заездом</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ОТОПЛЕНИЕ — ЭЛЕКТРИЧЕСКИЕ КОНВЕКТОРЫ</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="12" t="n"/>
+      <c r="D84" s="12" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="13" t="n">
+        <v>61000</v>
+      </c>
+      <c r="G84" s="14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H84" s="15" t="inlineStr"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>8. ВЕНТИЛЯЦИЯ И ВОДОСНАБЖЕНИЕ (внутренняя разводка)</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="6" t="n">
@@ -2745,7 +2749,7 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Запорная арматура, подводки, сифоны</t>
+          <t>Вентилятор вытяжной с/у + обратный клапан</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -2753,59 +2757,119 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Приточный клапан стеновой (если нет проветривания окнами)</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F88" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>опция; окна уже есть</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Труба ППР/металлопласт + фитинги (ХВС/ГВС)</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="E87" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F87" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G87" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ВЕНТИЛЯЦИЯ И ВОДОСНАБЖЕНИЕ (внутренняя разводка)</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="13" t="n">
-        <v>59300</v>
-      </c>
-      <c r="G88" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H88" s="15" t="inlineStr"/>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>9. САНТЕХНИКА С/У</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
+      <c r="E89" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>внутренняя разводка до точек</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Канализация ПВХ 50/110 + фитинги</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="7" t="inlineStr"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="6" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Унитаз-компакт с микролифтом</t>
+          <t>Водонагреватель накопительный 50–80 л</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -2817,23 +2881,27 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>если нет ГВС</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Раковина + тумба подвесная 50–60 см</t>
+          <t>Фильтр грубой очистки + редуктор</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -2845,27 +2913,23 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>16000</v>
+        <v>4500</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>16000</v>
+        <v>4500</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>габарит с/у 3,32 м²</t>
-        </is>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H92" s="7" t="inlineStr"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Смеситель раковины</t>
+          <t>Запорная арматура, подводки, сифоны</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -2873,103 +2937,51 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H93" s="7" t="inlineStr"/>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Душевая кабина / уголок 90×90 + поддон</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="n">
-        <v>28000</v>
-      </c>
-      <c r="F94" s="9" t="n">
-        <v>28000</v>
-      </c>
-      <c r="G94" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H94" s="7" t="inlineStr"/>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Смеситель душа / стойка (если не в комплекте)</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>5500</v>
-      </c>
-      <c r="F95" s="9" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G95" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H95" s="7" t="inlineStr"/>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Зеркало / шкафчик зеркальный</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F96" s="9" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G96" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H96" s="7" t="inlineStr"/>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ВЕНТИЛЯЦИЯ И ВОДОСНАБЖЕНИЕ (внутренняя разводка)</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="12" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="13" t="n">
+        <v>59300</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H94" s="15" t="inlineStr"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>9. САНТЕХНИКА С/У</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="6" t="n">
@@ -2977,7 +2989,7 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Аксессуары с/у (держатель, крючки, полка)</t>
+          <t>Унитаз-компакт с микролифтом</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
@@ -2985,17 +2997,17 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>3500</v>
+        <v>14000</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>3500</v>
+        <v>14000</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H97" s="7" t="inlineStr"/>
     </row>
@@ -3005,7 +3017,7 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Корзина для белья</t>
+          <t>Раковина + тумба подвесная 50–60 см</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
@@ -3013,59 +3025,115 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="7" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>Итого: САНТЕХНИКА С/У</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="12" t="n"/>
-      <c r="F99" s="13" t="n">
-        <v>80500</v>
-      </c>
-      <c r="G99" s="14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H99" s="15" t="inlineStr"/>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>10. КУХНЯ (мебель + техника)</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="5" t="n"/>
-    </row>
-    <row r="102" ht="32" customHeight="1">
+        <v>0.4</v>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>габарит с/у 3,32 м²</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Смеситель раковины</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Душевая кабина / уголок 90×90 + поддон</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>Смеситель душа / стойка (если не в комплекте)</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
       <c r="A102" s="6" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Кухонный гарнитур 2,4–2,7 м (корпуса + фасады)</t>
+          <t>Зеркало / шкафчик зеркальный</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -3073,55 +3141,55 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>85000</v>
+        <v>7000</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>85000</v>
+        <v>7000</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="H102" s="7" t="inlineStr"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Столешница + плинтус</t>
+          <t>Аксессуары с/у (держатель, крючки, полка)</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>6500</v>
+        <v>3500</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>19500</v>
+        <v>3500</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H103" s="7" t="inlineStr"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Мойка нерж. + смеситель кухня</t>
+          <t>Корзина для белья</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
@@ -3129,111 +3197,59 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H104" s="7" t="inlineStr"/>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Варочная панель электрическая 4 конф.</t>
-        </is>
-      </c>
-      <c r="C105" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F105" s="9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G105" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H105" s="7" t="inlineStr"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Духовой шкаф электрический</t>
-        </is>
-      </c>
-      <c r="C106" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="n">
-        <v>28000</v>
-      </c>
-      <c r="F106" s="9" t="n">
-        <v>28000</v>
-      </c>
-      <c r="G106" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H106" s="7" t="inlineStr"/>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Вытяжка</t>
-        </is>
-      </c>
-      <c r="C107" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G107" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H107" s="7" t="inlineStr"/>
-    </row>
-    <row r="108" ht="20" customHeight="1">
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Итого: САНТЕХНИКА С/У</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n"/>
+      <c r="C105" s="12" t="n"/>
+      <c r="D105" s="12" t="n"/>
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="13" t="n">
+        <v>80500</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H105" s="15" t="inlineStr"/>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>10. КУХНЯ (мебель + техника)</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+    </row>
+    <row r="108" ht="32" customHeight="1">
       <c r="A108" s="6" t="n">
         <v>75</v>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Холодильник двухкамерный</t>
+          <t>Кухонный гарнитур 2,4–2,7 м (корпуса + фасады)</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
@@ -3241,17 +3257,17 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="G108" s="10" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="H108" s="7" t="inlineStr"/>
     </row>
@@ -3261,25 +3277,25 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>СВЧ</t>
+          <t>Столешница + плинтус</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>9000</v>
+        <v>6500</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>9000</v>
+        <v>19500</v>
       </c>
       <c r="G109" s="10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H109" s="7" t="inlineStr"/>
     </row>
@@ -3289,7 +3305,7 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Посудомоечная машина 45 см</t>
+          <t>Мойка нерж. + смеситель кухня</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -3297,23 +3313,19 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>35000</v>
+        <v>12000</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>35000</v>
+        <v>12000</v>
       </c>
       <c r="G110" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H110" s="7" t="inlineStr">
-        <is>
-          <t>для посуточной очень желательно</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="6" t="n">
@@ -3321,7 +3333,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Стиральная машина 6–7 кг</t>
+          <t>Варочная панель электрическая 4 конф.</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
@@ -3333,55 +3345,107 @@
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>32000</v>
+        <v>18000</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>32000</v>
+        <v>18000</v>
       </c>
       <c r="G111" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H111" s="7" t="inlineStr"/>
     </row>
-    <row r="112">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>Итого: КУХНЯ (мебель + техника)</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="n"/>
-      <c r="C112" s="12" t="n"/>
-      <c r="D112" s="12" t="n"/>
-      <c r="E112" s="12" t="n"/>
-      <c r="F112" s="13" t="n">
-        <v>295500</v>
-      </c>
-      <c r="G112" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H112" s="15" t="inlineStr"/>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>11. МЕБЕЛЬ — КУХНЯ-ГОСТИНАЯ + ПРИХОЖАЯ</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="5" t="n"/>
-      <c r="F114" s="5" t="n"/>
-      <c r="G114" s="5" t="n"/>
-      <c r="H114" s="5" t="n"/>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Духовой шкаф электрический</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>28000</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Вытяжка</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Холодильник двухкамерный</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H114" s="7" t="inlineStr"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="6" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Диван-кровать раскладной 140–160</t>
+          <t>СВЧ</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -3393,27 +3457,23 @@
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>45000</v>
+        <v>9000</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>45000</v>
+        <v>9000</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>доп. спальное место</t>
-        </is>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="H115" s="7" t="inlineStr"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="6" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Кресло / пуф</t>
+          <t>Посудомоечная машина 45 см</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -3425,23 +3485,27 @@
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>8000</v>
+        <v>35000</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>8000</v>
+        <v>35000</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H116" s="7" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>для посуточной очень желательно</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="6" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Журнальный столик</t>
+          <t>Стиральная машина 6–7 кг</t>
         </is>
       </c>
       <c r="C117" s="8" t="n">
@@ -3453,99 +3517,47 @@
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>6000</v>
+        <v>32000</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>6000</v>
+        <v>32000</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H117" s="7" t="inlineStr"/>
     </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Тумба ТВ</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F118" s="9" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G118" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>Обеденный стол на 4–6 чел.</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G119" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H119" s="7" t="inlineStr"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Стул обеденный</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="n">
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Итого: КУХНЯ (мебель + техника)</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="n"/>
+      <c r="C118" s="12" t="n"/>
+      <c r="D118" s="12" t="n"/>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="13" t="n">
+        <v>295500</v>
+      </c>
+      <c r="G118" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G120" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H120" s="7" t="inlineStr"/>
+      <c r="H118" s="15" t="inlineStr"/>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>11. МЕБЕЛЬ — КУХНЯ-ГОСТИНАЯ + ПРИХОЖАЯ</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="6" t="n">
@@ -3553,7 +3565,7 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Стеллаж / шкаф открытый</t>
+          <t>Диван-кровать раскладной 140–160</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
@@ -3565,15 +3577,19 @@
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>10000</v>
+        <v>45000</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>10000</v>
+        <v>45000</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H121" s="7" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>доп. спальное место</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="6" t="n">
@@ -3581,7 +3597,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Зеркало + вешалка + обувница (прихожая)</t>
+          <t>Кресло / пуф</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
@@ -3589,63 +3605,115 @@
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="G122" s="10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H122" s="7" t="inlineStr"/>
     </row>
-    <row r="123">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>Итого: МЕБЕЛЬ — КУХНЯ-ГОСТИНАЯ + ПРИХОЖАЯ</t>
-        </is>
-      </c>
-      <c r="B123" s="12" t="n"/>
-      <c r="C123" s="12" t="n"/>
-      <c r="D123" s="12" t="n"/>
-      <c r="E123" s="12" t="n"/>
-      <c r="F123" s="13" t="n">
-        <v>111000</v>
-      </c>
-      <c r="G123" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H123" s="15" t="inlineStr"/>
-    </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>12. МЕБЕЛЬ — СПАЛЬНИ (2 × 9,21 м²)</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="n"/>
-      <c r="C125" s="5" t="n"/>
-      <c r="D125" s="5" t="n"/>
-      <c r="E125" s="5" t="n"/>
-      <c r="F125" s="5" t="n"/>
-      <c r="G125" s="5" t="n"/>
-      <c r="H125" s="5" t="n"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Журнальный столик</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Тумба ТВ</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F124" s="9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Обеденный стол на 4–6 чел.</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H125" s="7" t="inlineStr"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="6" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Кровать 160×200 с основанием (спальня 1)</t>
+          <t>Стул обеденный</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
@@ -3653,23 +3721,23 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>22000</v>
+        <v>3500</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="G126" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H126" s="7" t="inlineStr"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Матрас ортопедический 160×200</t>
+          <t>Стеллаж / шкаф открытый</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
@@ -3681,23 +3749,23 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="G127" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H127" s="7" t="inlineStr"/>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="6" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Кровать 140×200 с основанием (спальня 2)</t>
+          <t>Зеркало + вешалка + обувница (прихожая)</t>
         </is>
       </c>
       <c r="C128" s="8" t="n">
@@ -3705,103 +3773,51 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="G128" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="H128" s="7" t="inlineStr"/>
     </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>Матрас 140×200</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="n">
-        <v>14000</v>
-      </c>
-      <c r="F129" s="9" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G129" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H129" s="7" t="inlineStr"/>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="n">
-        <v>91</v>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>Тумба прикроватная</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E130" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F130" s="9" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G130" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H130" s="7" t="inlineStr"/>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>Шкаф 2-дверный</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F131" s="9" t="n">
-        <v>44000</v>
-      </c>
-      <c r="G131" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H131" s="7" t="inlineStr"/>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>Итого: МЕБЕЛЬ — КУХНЯ-ГОСТИНАЯ + ПРИХОЖАЯ</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="n"/>
+      <c r="C129" s="12" t="n"/>
+      <c r="D129" s="12" t="n"/>
+      <c r="E129" s="12" t="n"/>
+      <c r="F129" s="13" t="n">
+        <v>111000</v>
+      </c>
+      <c r="G129" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H129" s="15" t="inlineStr"/>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>12. МЕБЕЛЬ — СПАЛЬНИ (2 × 9,21 м²)</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="5" t="n"/>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="6" t="n">
@@ -3809,7 +3825,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Комод</t>
+          <t>Кровать 160×200 с основанием (спальня 1)</t>
         </is>
       </c>
       <c r="C132" s="8" t="n">
@@ -3821,13 +3837,13 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="G132" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H132" s="7" t="inlineStr"/>
     </row>
@@ -3837,11 +3853,11 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Зеркало настенное</t>
+          <t>Матрас ортопедический 160×200</t>
         </is>
       </c>
       <c r="C133" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
@@ -3849,59 +3865,111 @@
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>2500</v>
+        <v>18000</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="G133" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H133" s="7" t="inlineStr"/>
     </row>
-    <row r="134">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>Итого: МЕБЕЛЬ — СПАЛЬНИ (2 × 9,21 м²)</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="n"/>
-      <c r="C134" s="12" t="n"/>
-      <c r="D134" s="12" t="n"/>
-      <c r="E134" s="12" t="n"/>
-      <c r="F134" s="13" t="n">
-        <v>145000</v>
-      </c>
-      <c r="G134" s="14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H134" s="15" t="inlineStr"/>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>13. ТЕХНИКА И ЭЛЕКТРОНИКА ДЛЯ ГОСТЕЙ</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="n"/>
-      <c r="E136" s="5" t="n"/>
-      <c r="F136" s="5" t="n"/>
-      <c r="G136" s="5" t="n"/>
-      <c r="H136" s="5" t="n"/>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Кровать 140×200 с основанием (спальня 2)</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F134" s="9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Матрас 140×200</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>Тумба прикроватная</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H136" s="7" t="inlineStr"/>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="6" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Телевизор Smart TV 43–50"</t>
+          <t>Шкаф 2-дверный</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
@@ -3909,27 +3977,23 @@
         </is>
       </c>
       <c r="E137" s="9" t="n">
-        <v>32000</v>
+        <v>22000</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>32000</v>
+        <v>44000</v>
       </c>
       <c r="G137" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H137" s="7" t="inlineStr">
-        <is>
-          <t>гостиная</t>
-        </is>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="H137" s="7" t="inlineStr"/>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="6" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Роутер Wi-Fi</t>
+          <t>Комод</t>
         </is>
       </c>
       <c r="C138" s="8" t="n">
@@ -3937,139 +4001,79 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E138" s="9" t="n">
-        <v>5500</v>
+        <v>10000</v>
       </c>
       <c r="F138" s="9" t="n">
-        <v>5500</v>
+        <v>10000</v>
       </c>
       <c r="G138" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="H138" s="7" t="inlineStr">
-        <is>
-          <t>обязательно</t>
-        </is>
-      </c>
+      <c r="H138" s="7" t="inlineStr"/>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="6" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Кондиционер сплит 9–12k BTU (гостиная)</t>
+          <t>Зеркало настенное</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E139" s="9" t="n">
-        <v>45000</v>
+        <v>2500</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>45000</v>
+        <v>5000</v>
       </c>
       <c r="G139" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>лето — критично для сдачи</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="n">
-        <v>98</v>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>Фен</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F140" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G140" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" s="7" t="inlineStr"/>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>Утюг + гладильная доска</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E141" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F141" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G141" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H141" s="7" t="inlineStr"/>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>Чайник электрический</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F142" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G142" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" s="7" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="H139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>Итого: МЕБЕЛЬ — СПАЛЬНИ (2 × 9,21 м²)</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="n"/>
+      <c r="C140" s="12" t="n"/>
+      <c r="D140" s="12" t="n"/>
+      <c r="E140" s="12" t="n"/>
+      <c r="F140" s="13" t="n">
+        <v>145000</v>
+      </c>
+      <c r="G140" s="14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H140" s="15" t="inlineStr"/>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>13. ТЕХНИКА И ЭЛЕКТРОНИКА ДЛЯ ГОСТЕЙ</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="5" t="n"/>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="5" t="n"/>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="6" t="n">
@@ -4077,7 +4081,7 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Кофемашина капсульная / тостер</t>
+          <t>Телевизор Smart TV 43–50"</t>
         </is>
       </c>
       <c r="C143" s="8" t="n">
@@ -4089,15 +4093,19 @@
         </is>
       </c>
       <c r="E143" s="9" t="n">
-        <v>8000</v>
+        <v>32000</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>8000</v>
+        <v>32000</v>
       </c>
       <c r="G143" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" s="7" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>гостиная</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="6" t="n">
@@ -4105,7 +4113,7 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Пылесос</t>
+          <t>Роутер Wi-Fi</t>
         </is>
       </c>
       <c r="C144" s="8" t="n">
@@ -4113,95 +4121,151 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E144" s="9" t="n">
-        <v>7000</v>
+        <v>5500</v>
       </c>
       <c r="F144" s="9" t="n">
-        <v>7000</v>
+        <v>5500</v>
       </c>
       <c r="G144" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>обязательно</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>Кондиционер сплит 9–12k BTU (гостиная)</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>лето — критично для сдачи</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>Фен</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G146" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H144" s="7" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ТЕХНИКА И ЭЛЕКТРОНИКА ДЛЯ ГОСТЕЙ</t>
-        </is>
-      </c>
-      <c r="B145" s="12" t="n"/>
-      <c r="C145" s="12" t="n"/>
-      <c r="D145" s="12" t="n"/>
-      <c r="E145" s="12" t="n"/>
-      <c r="F145" s="13" t="n">
-        <v>107000</v>
-      </c>
-      <c r="G145" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H145" s="15" t="inlineStr"/>
-    </row>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>14. ТЕКСТИЛЬ, ПОСТЕЛЬ, ШТОРЫ</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="n"/>
-      <c r="C147" s="5" t="n"/>
-      <c r="D147" s="5" t="n"/>
-      <c r="E147" s="5" t="n"/>
-      <c r="F147" s="5" t="n"/>
-      <c r="G147" s="5" t="n"/>
-      <c r="H147" s="5" t="n"/>
-    </row>
-    <row r="148" ht="32" customHeight="1">
+      <c r="H146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>Утюг + гладильная доска</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F147" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G147" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
       <c r="A148" s="6" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Комплект постельного белья (основной + сменный)</t>
+          <t>Чайник электрический</t>
         </is>
       </c>
       <c r="C148" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E148" s="9" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="F148" s="9" t="n">
-        <v>21000</v>
+        <v>2500</v>
       </c>
       <c r="G148" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>3 спальных места × 2</t>
-        </is>
-      </c>
+      <c r="H148" s="7" t="inlineStr"/>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="6" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Одеяло всесезонное</t>
+          <t>Кофемашина капсульная / тостер</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
@@ -4209,10 +4273,10 @@
         </is>
       </c>
       <c r="E149" s="9" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="G149" s="10" t="n">
         <v>0</v>
@@ -4221,15 +4285,15 @@
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="6" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>Подушка</t>
+          <t>Пылесос</t>
         </is>
       </c>
       <c r="C150" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
@@ -4237,103 +4301,47 @@
         </is>
       </c>
       <c r="E150" s="9" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
       <c r="F150" s="9" t="n">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="G150" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H150" s="7" t="inlineStr"/>
     </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>Наматрасник непромокаемый</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F151" s="9" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G151" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>для аренды обязательно</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="6" t="n">
-        <v>107</v>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>Покрывало / плед</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F152" s="9" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G152" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" s="7" t="inlineStr"/>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="6" t="n">
-        <v>108</v>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>Шторы блэкаут + тюль (спальни)</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F153" s="9" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G153" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H153" s="7" t="inlineStr"/>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ТЕХНИКА И ЭЛЕКТРОНИКА ДЛЯ ГОСТЕЙ</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n"/>
+      <c r="C151" s="12" t="n"/>
+      <c r="D151" s="12" t="n"/>
+      <c r="E151" s="12" t="n"/>
+      <c r="F151" s="13" t="n">
+        <v>107000</v>
+      </c>
+      <c r="G151" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H151" s="15" t="inlineStr"/>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>14. ТЕКСТИЛЬ, ПОСТЕЛЬ, ШТОРЫ</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="5" t="n"/>
     </row>
     <row r="154" ht="32" customHeight="1">
       <c r="A154" s="6" t="n">
@@ -4341,11 +4349,11 @@
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>Шторы / римская (гостиная, на существующие окна)</t>
+          <t>Комплект постельного белья (основной + сменный)</t>
         </is>
       </c>
       <c r="C154" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
@@ -4353,15 +4361,19 @@
         </is>
       </c>
       <c r="E154" s="9" t="n">
-        <v>9000</v>
+        <v>3500</v>
       </c>
       <c r="F154" s="9" t="n">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="G154" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H154" s="7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>3 спальных места × 2</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="6" t="n">
@@ -4369,11 +4381,11 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>Карнизы</t>
+          <t>Одеяло всесезонное</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
@@ -4381,13 +4393,13 @@
         </is>
       </c>
       <c r="E155" s="9" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="G155" s="10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H155" s="7" t="inlineStr"/>
     </row>
@@ -4397,7 +4409,7 @@
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>Полотенца банные</t>
+          <t>Подушка</t>
         </is>
       </c>
       <c r="C156" s="8" t="n">
@@ -4409,10 +4421,10 @@
         </is>
       </c>
       <c r="E156" s="9" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="F156" s="9" t="n">
-        <v>4800</v>
+        <v>9000</v>
       </c>
       <c r="G156" s="10" t="n">
         <v>0</v>
@@ -4425,11 +4437,11 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Полотенца лицевые</t>
+          <t>Наматрасник непромокаемый</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
@@ -4437,15 +4449,19 @@
         </is>
       </c>
       <c r="E157" s="9" t="n">
-        <v>400</v>
+        <v>2500</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>2400</v>
+        <v>7500</v>
       </c>
       <c r="G157" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H157" s="7" t="inlineStr"/>
+      <c r="H157" s="7" t="inlineStr">
+        <is>
+          <t>для аренды обязательно</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="6" t="n">
@@ -4453,11 +4469,11 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>Коврик с/у + прикроватные</t>
+          <t>Покрывало / плед</t>
         </is>
       </c>
       <c r="C158" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
@@ -4465,10 +4481,10 @@
         </is>
       </c>
       <c r="E158" s="9" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>4800</v>
+        <v>9000</v>
       </c>
       <c r="G158" s="10" t="n">
         <v>0</v>
@@ -4481,82 +4497,134 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Скатерть / дорожка</t>
+          <t>Шторы блэкаут + тюль (спальни)</t>
         </is>
       </c>
       <c r="C159" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E159" s="9" t="n">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>1500</v>
+        <v>16000</v>
       </c>
       <c r="G159" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160" ht="32" customHeight="1">
+      <c r="A160" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>Шторы / римская (гостиная, на существующие окна)</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E160" s="9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F160" s="9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G160" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>Карнизы</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F161" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G161" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>Полотенца банные</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="F162" s="9" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G162" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H159" s="7" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ТЕКСТИЛЬ, ПОСТЕЛЬ, ШТОРЫ</t>
-        </is>
-      </c>
-      <c r="B160" s="12" t="n"/>
-      <c r="C160" s="12" t="n"/>
-      <c r="D160" s="12" t="n"/>
-      <c r="E160" s="12" t="n"/>
-      <c r="F160" s="13" t="n">
-        <v>105000</v>
-      </c>
-      <c r="G160" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H160" s="15" t="inlineStr"/>
-    </row>
-    <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>15. ПОСУДА, БЫТ, СТАРТ ДЛЯ ПОСУТОЧНОЙ</t>
-        </is>
-      </c>
-      <c r="B162" s="5" t="n"/>
-      <c r="C162" s="5" t="n"/>
-      <c r="D162" s="5" t="n"/>
-      <c r="E162" s="5" t="n"/>
-      <c r="F162" s="5" t="n"/>
-      <c r="G162" s="5" t="n"/>
-      <c r="H162" s="5" t="n"/>
+      <c r="H162" s="7" t="inlineStr"/>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="6" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Сервиз тарелок/мисок на 6 персон</t>
+          <t>Полотенца лицевые</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E163" s="9" t="n">
-        <v>5000</v>
+        <v>400</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>5000</v>
+        <v>2400</v>
       </c>
       <c r="G163" s="10" t="n">
         <v>0</v>
@@ -4565,26 +4633,26 @@
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="6" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>Кружки, бокалы, стаканы</t>
+          <t>Коврик с/у + прикроватные</t>
         </is>
       </c>
       <c r="C164" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E164" s="9" t="n">
-        <v>3500</v>
+        <v>1200</v>
       </c>
       <c r="F164" s="9" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="G164" s="10" t="n">
         <v>0</v>
@@ -4593,11 +4661,11 @@
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Столовые приборы на 6 + запас</t>
+          <t>Скатерть / дорожка</t>
         </is>
       </c>
       <c r="C165" s="8" t="n">
@@ -4605,103 +4673,51 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E165" s="9" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G165" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H165" s="7" t="inlineStr"/>
     </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>Кастрюли, сковороды, ножи, доски, лопатки</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F166" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G166" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" s="7" t="inlineStr"/>
-    </row>
-    <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="6" t="n">
-        <v>119</v>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>Контейнеры, открывалки и пр.</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F167" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G167" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="7" t="inlineStr"/>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>Сушилка для посуды, ведро для мусора</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E168" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F168" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G168" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="7" t="inlineStr"/>
+    <row r="166">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ТЕКСТИЛЬ, ПОСТЕЛЬ, ШТОРЫ</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="n"/>
+      <c r="C166" s="12" t="n"/>
+      <c r="D166" s="12" t="n"/>
+      <c r="E166" s="12" t="n"/>
+      <c r="F166" s="13" t="n">
+        <v>105000</v>
+      </c>
+      <c r="G166" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H166" s="15" t="inlineStr"/>
+    </row>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>15. ПОСУДА, БЫТ, СТАРТ ДЛЯ ПОСУТОЧНОЙ</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="5" t="n"/>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="6" t="n">
@@ -4709,22 +4725,22 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>Вешалки плечики</t>
+          <t>Сервиз тарелок/мисок на 6 персон</t>
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E169" s="9" t="n">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="G169" s="10" t="n">
         <v>0</v>
@@ -4737,7 +4753,7 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>Расходники старт (пакеты, губки, мешки)</t>
+          <t>Кружки, бокалы, стаканы</t>
         </is>
       </c>
       <c r="C170" s="8" t="n">
@@ -4749,10 +4765,10 @@
         </is>
       </c>
       <c r="E170" s="9" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="G170" s="10" t="n">
         <v>0</v>
@@ -4765,7 +4781,7 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Старт гигиена: бумага, мыло, шампунь, гель</t>
+          <t>Столовые приборы на 6 + запас</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
@@ -4777,10 +4793,10 @@
         </is>
       </c>
       <c r="E171" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G171" s="10" t="n">
         <v>0</v>
@@ -4793,7 +4809,7 @@
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>Аптечка + огнетушитель + датчик дыма</t>
+          <t>Кастрюли, сковороды, ножи, доски, лопатки</t>
         </is>
       </c>
       <c r="C172" s="8" t="n">
@@ -4805,13 +4821,13 @@
         </is>
       </c>
       <c r="E172" s="9" t="n">
-        <v>4500</v>
+        <v>8000</v>
       </c>
       <c r="F172" s="9" t="n">
-        <v>4500</v>
+        <v>8000</v>
       </c>
       <c r="G172" s="10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H172" s="7" t="inlineStr"/>
     </row>
@@ -4821,7 +4837,7 @@
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Сушилка для белья</t>
+          <t>Контейнеры, открывалки и пр.</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
@@ -4829,14 +4845,14 @@
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E173" s="9" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G173" s="10" t="n">
         <v>0</v>
@@ -4849,7 +4865,7 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Коврик грязезащитный у входа (внутри)</t>
+          <t>Сушилка для посуды, ведро для мусора</t>
         </is>
       </c>
       <c r="C174" s="8" t="n">
@@ -4857,7 +4873,7 @@
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E174" s="9" t="n">
@@ -4871,45 +4887,97 @@
       </c>
       <c r="H174" s="7" t="inlineStr"/>
     </row>
-    <row r="175">
-      <c r="A175" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ПОСУДА, БЫТ, СТАРТ ДЛЯ ПОСУТОЧНОЙ</t>
-        </is>
-      </c>
-      <c r="B175" s="12" t="n"/>
-      <c r="C175" s="12" t="n"/>
-      <c r="D175" s="12" t="n"/>
-      <c r="E175" s="12" t="n"/>
-      <c r="F175" s="13" t="n">
-        <v>40500</v>
-      </c>
-      <c r="G175" s="14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H175" s="15" t="inlineStr"/>
-    </row>
-    <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>16. ДЕКОР И ПРОЧЕЕ ДЛЯ СДАЧИ</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="5" t="n"/>
-      <c r="D177" s="5" t="n"/>
-      <c r="E177" s="5" t="n"/>
-      <c r="F177" s="5" t="n"/>
-      <c r="G177" s="5" t="n"/>
-      <c r="H177" s="5" t="n"/>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>Вешалки плечики</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F175" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>Расходники старт (пакеты, губки, мешки)</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F176" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G176" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Старт гигиена: бумага, мыло, шампунь, гель</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F177" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G177" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="7" t="inlineStr"/>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="6" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Картины / постеры</t>
+          <t>Аптечка + огнетушитель + датчик дыма</t>
         </is>
       </c>
       <c r="C178" s="8" t="n">
@@ -4921,10 +4989,10 @@
         </is>
       </c>
       <c r="E178" s="9" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F178" s="9" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="G178" s="10" t="n">
         <v>0.2</v>
@@ -4933,11 +5001,11 @@
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="6" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Декор / растения искусственные</t>
+          <t>Сушилка для белья</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
@@ -4945,31 +5013,31 @@
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="E179" s="9" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="G179" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="7" t="inlineStr"/>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="6" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Лампа прикроватная / торшер</t>
+          <t>Коврик грязезащитный у входа (внутри)</t>
         </is>
       </c>
       <c r="C180" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
@@ -4980,96 +5048,44 @@
         <v>2500</v>
       </c>
       <c r="F180" s="9" t="n">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="G180" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ПОСУДА, БЫТ, СТАРТ ДЛЯ ПОСУТОЧНОЙ</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="n"/>
+      <c r="C181" s="12" t="n"/>
+      <c r="D181" s="12" t="n"/>
+      <c r="E181" s="12" t="n"/>
+      <c r="F181" s="13" t="n">
+        <v>40500</v>
+      </c>
+      <c r="G181" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="H180" s="7" t="inlineStr"/>
-    </row>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="6" t="n">
-        <v>130</v>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>Органайзеры для белья</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E181" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F181" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G181" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="7" t="inlineStr"/>
-    </row>
-    <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="6" t="n">
-        <v>131</v>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>Сейф небольшой (для хозяина)</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="E182" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F182" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G182" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H182" s="7" t="inlineStr"/>
-    </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>Ключница + кейбокс / запасные ключи</t>
-        </is>
-      </c>
-      <c r="C183" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D183" s="6" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F183" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="G183" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H183" s="7" t="inlineStr"/>
+      <c r="H181" s="15" t="inlineStr"/>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>16. ДЕКОР И ПРОЧЕЕ ДЛЯ СДАЧИ</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="5" t="n"/>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="6" t="n">
@@ -5077,7 +5093,7 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>Табличка Wi-Fi / правила дома</t>
+          <t>Картины / постеры</t>
         </is>
       </c>
       <c r="C184" s="8" t="n">
@@ -5089,13 +5105,13 @@
         </is>
       </c>
       <c r="E184" s="9" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F184" s="9" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="G184" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H184" s="7" t="inlineStr"/>
     </row>
@@ -5105,7 +5121,7 @@
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>Запас: лампочки, батарейки, фильтры</t>
+          <t>Декор / растения искусственные</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
@@ -5117,13 +5133,13 @@
         </is>
       </c>
       <c r="E185" s="9" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F185" s="9" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G185" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H185" s="7" t="inlineStr"/>
     </row>
@@ -5133,67 +5149,119 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>Клининг-набор старт (химия, швабра, тряпки)</t>
+          <t>Лампа прикроватная / торшер</t>
         </is>
       </c>
       <c r="C186" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E186" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F186" s="9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G186" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>Органайзеры для белья</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
           <t>компл.</t>
         </is>
       </c>
-      <c r="E186" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F186" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G186" s="10" t="n">
+      <c r="E187" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F187" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G187" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H186" s="7" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="11" t="inlineStr">
-        <is>
-          <t>Итого: ДЕКОР И ПРОЧЕЕ ДЛЯ СДАЧИ</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="n"/>
-      <c r="C187" s="12" t="n"/>
-      <c r="D187" s="12" t="n"/>
-      <c r="E187" s="12" t="n"/>
-      <c r="F187" s="13" t="n">
-        <v>36500</v>
-      </c>
-      <c r="G187" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H187" s="15" t="inlineStr"/>
-    </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>17. РЕЗЕРВ (доставка и неучтённое)</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="n"/>
-      <c r="C189" s="5" t="n"/>
-      <c r="D189" s="5" t="n"/>
-      <c r="E189" s="5" t="n"/>
-      <c r="F189" s="5" t="n"/>
-      <c r="G189" s="5" t="n"/>
-      <c r="H189" s="5" t="n"/>
+      <c r="H187" s="7" t="inlineStr"/>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>Сейф небольшой (для хозяина)</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E188" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F188" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G188" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>Ключница + кейбокс / запасные ключи</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F189" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G189" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H189" s="7" t="inlineStr"/>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="6" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>Доставка материалов</t>
+          <t>Табличка Wi-Fi / правила дома</t>
         </is>
       </c>
       <c r="C190" s="8" t="n">
@@ -5201,14 +5269,14 @@
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>усл.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E190" s="9" t="n">
-        <v>20000</v>
+        <v>1500</v>
       </c>
       <c r="F190" s="9" t="n">
-        <v>20000</v>
+        <v>1500</v>
       </c>
       <c r="G190" s="10" t="n">
         <v>0</v>
@@ -5217,11 +5285,11 @@
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="6" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>Резерв на крепёж / доборы / отходы 5%</t>
+          <t>Запас: лампочки, батарейки, фильтры</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
@@ -5229,108 +5297,224 @@
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>усл.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="E191" s="9" t="n">
-        <v>35000</v>
+        <v>2000</v>
       </c>
       <c r="F191" s="9" t="n">
-        <v>35000</v>
+        <v>2000</v>
       </c>
       <c r="G191" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H191" s="7" t="inlineStr"/>
     </row>
-    <row r="192">
-      <c r="A192" s="11" t="inlineStr">
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>Клининг-набор старт (химия, швабра, тряпки)</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="E192" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F192" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G192" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="7" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>Итого: ДЕКОР И ПРОЧЕЕ ДЛЯ СДАЧИ</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="n"/>
+      <c r="C193" s="12" t="n"/>
+      <c r="D193" s="12" t="n"/>
+      <c r="E193" s="12" t="n"/>
+      <c r="F193" s="13" t="n">
+        <v>36500</v>
+      </c>
+      <c r="G193" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H193" s="15" t="inlineStr"/>
+    </row>
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>17. РЕЗЕРВ (доставка и неучтённое)</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="5" t="n"/>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>Доставка материалов</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>усл.</t>
+        </is>
+      </c>
+      <c r="E196" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F196" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G196" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="7" t="inlineStr"/>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>Резерв на крепёж / доборы / отходы 5%</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>усл.</t>
+        </is>
+      </c>
+      <c r="E197" s="9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F197" s="9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G197" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" s="7" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="11" t="inlineStr">
         <is>
           <t>Итого: РЕЗЕРВ (доставка и неучтённое)</t>
         </is>
       </c>
-      <c r="B192" s="12" t="n"/>
-      <c r="C192" s="12" t="n"/>
-      <c r="D192" s="12" t="n"/>
-      <c r="E192" s="12" t="n"/>
-      <c r="F192" s="13" t="n">
+      <c r="B198" s="12" t="n"/>
+      <c r="C198" s="12" t="n"/>
+      <c r="D198" s="12" t="n"/>
+      <c r="E198" s="12" t="n"/>
+      <c r="F198" s="13" t="n">
         <v>55000</v>
       </c>
-      <c r="G192" s="14" t="n">
+      <c r="G198" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H192" s="15" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="17" t="inlineStr">
+      <c r="H198" s="15" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="17" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ И КОМПЛЕКТАЦИЯ (только внутрянка)</t>
         </is>
       </c>
-      <c r="B194" s="17" t="n"/>
-      <c r="C194" s="17" t="n"/>
-      <c r="D194" s="17" t="n"/>
-      <c r="E194" s="17" t="n"/>
-      <c r="F194" s="18" t="n">
-        <v>1587550</v>
-      </c>
-      <c r="G194" s="19" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="H194" s="20" t="inlineStr">
+      <c r="B200" s="17" t="n"/>
+      <c r="C200" s="17" t="n"/>
+      <c r="D200" s="17" t="n"/>
+      <c r="E200" s="17" t="n"/>
+      <c r="F200" s="18" t="n">
+        <v>1671450</v>
+      </c>
+      <c r="G200" s="19" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H200" s="20" t="inlineStr">
         <is>
           <t>сумма дней по позициям (часть работ параллельно)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="40" customHeight="1">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>Ориентир календаря внутрянки бригадой 2 чел.: ≈ 32 раб. дней. Работы в смету НЕ входят. Итого материалы+обстановка: ≈ 1 587 550 ₽. С запасом 10%: ≈ 1 746 305 ₽. Не включено: окна  терраса  фасад  кровля  наружные работы.</t>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Ориентир календаря внутрянки бригадой 2 чел.: ≈ 32 раб. дней. Работы в смету НЕ входят. Итого материалы+обстановка: ≈ 1 671 450 ₽. С запасом 10%: ≈ 1 838 595 ₽. Не включено: окна  терраса  фасад  кровля  наружные работы.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A114:H114"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A166:E166"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A201:H201"/>
+    <mergeCell ref="A107:H107"/>
+    <mergeCell ref="A142:H142"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A168:H168"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A162:H162"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A187:E187"/>
-    <mergeCell ref="A177:H177"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A189:H189"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A145:E145"/>
-    <mergeCell ref="A192:E192"/>
+    <mergeCell ref="A153:H153"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A183:H183"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A198:E198"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A136:H136"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A129:E129"/>
     <mergeCell ref="A195:H195"/>
-    <mergeCell ref="A160:E160"/>
-    <mergeCell ref="A194:E194"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A147:H147"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A181:E181"/>
+    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A200:E200"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5384,33 +5568,33 @@
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>ОТДЕЛКА ПЕРЕГОРОДОК И СТЕН ИЗНУТРИ (каркас уже есть)</t>
+          <t>ОТДЕЛКА СТЕН ВАГОНКОЙ (как на фото, без ГКЛ)</t>
         </is>
       </c>
       <c r="B4" s="23" t="n">
-        <v>134920</v>
+        <v>185710</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="D4" s="24" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>ПОТОЛКИ</t>
+          <t>ПОТОЛКИ ВАГОНКОЙ (как на фото, без ГКЛ)</t>
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>48480</v>
+        <v>59740</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="6">
@@ -5423,7 +5607,7 @@
         <v>103500</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>4.4</v>
@@ -5439,7 +5623,7 @@
         <v>42360</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>2.7</v>
@@ -5455,7 +5639,7 @@
         <v>39400</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>1.1</v>
@@ -5468,13 +5652,13 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>122590</v>
+        <v>144440</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="10">
@@ -5487,7 +5671,7 @@
         <v>61000</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>1.7</v>
@@ -5503,7 +5687,7 @@
         <v>59300</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>3.9</v>
@@ -5519,7 +5703,7 @@
         <v>80500</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>2.3</v>
@@ -5535,7 +5719,7 @@
         <v>295500</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>18.6</v>
+        <v>17.7</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>4</v>
@@ -5551,7 +5735,7 @@
         <v>111000</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1.5</v>
@@ -5567,7 +5751,7 @@
         <v>145000</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2.3</v>
@@ -5583,7 +5767,7 @@
         <v>107000</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1.5</v>
@@ -5599,7 +5783,7 @@
         <v>105000</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1.1</v>
@@ -5615,7 +5799,7 @@
         <v>40500</v>
       </c>
       <c r="C18" s="24" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>0.2</v>
@@ -5631,7 +5815,7 @@
         <v>36500</v>
       </c>
       <c r="C19" s="24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>0.7</v>
@@ -5647,7 +5831,7 @@
         <v>55000</v>
       </c>
       <c r="C20" s="24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>0</v>
@@ -5660,13 +5844,13 @@
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>1587550</v>
+        <v>1671450</v>
       </c>
       <c r="C21" s="17" t="n">
         <v>100</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>47.9</v>
+        <v>48.6</v>
       </c>
     </row>
   </sheetData>
@@ -6088,46 +6272,70 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Отопление</t>
+          <t>Отделка стен/потолков</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>Электрические конвекторы (5 шт. + полотенцесушитель)</t>
+          <t>Вагонка штиль белая (как на фото) — без ГКЛ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Смета включает</t>
+          <t>Отопление</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>Только внутренняя отделка + инженерия внутри + обстановка под посуточную</t>
+          <t>Электрические конвекторы (5 шт. + полотенцесушитель)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Смета НЕ включает</t>
+          <t>Уличное освещение</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>Окна, терраса, фасад, кровля, фундамент, наружные работы, стоимость монтажа</t>
+          <t>Включено: 3 настенных + 2 прожектора + датчик</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
+          <t>Смета включает</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Внутренняя отделка вагонкой + инженерия + уличная подсветка + обстановка</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Смета НЕ включает</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Окна, настил террасы, фасад, кровля, фундамент, стоимость монтажа</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
           <t>Вместимость</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>4–6 гостей</t>
         </is>

--- a/smeta/Smeta_karkasnyi_dom_posutochno.xlsx
+++ b/smeta/Smeta_karkasnyi_dom_posutochno.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Смета" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Сводка по разделам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Обстановка по комнатам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Исходные данные" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Сравнение вагонка vs МДФ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Обстановка по комнатам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Исходные данные" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -171,11 +172,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5868,6 +5873,215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Сравнение отделки: вагонка vs МДФ-панели (пол — ламинат, без изменений)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Смета по умолчанию сейчас на ВАГОНКЕ. Ниже — сколько сэкономите, если стены/потолки сделать МДФ-панелями. Полы (ламинат), с/у (плитка), инженерия и мебель — одинаковые.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Вагонка (текущая смета)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>МДФ панели</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>МДФ эконом</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Стены (материалы)</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>185710</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>128010</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>103810</v>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>МДФ без покраски — уже в пленке</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Потолки (материалы)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>59740</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>38360</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>31640</v>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>МДФ без покраски</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Итого стены+потолки</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>245450</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>166370</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>135450</v>
+      </c>
+      <c r="E7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Полы ламинат</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>103500</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>103500</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>103500</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>одинаково во всех вариантах</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>ВСЯ СМЕТА дома</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>1671450</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>1592370</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>1561450</v>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>остальные разделы без изменений</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Экономия vs вагонка</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>79080</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>МДФ дешевле отделки на 32% / эконом на 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Плюсы / минусы</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>ВАГОНКА: теплее на вид и на ощупь, лучше для «домашнего» фото посуточной, можно перекрасить; дороже, нужна покраска, дольше монтаж.
+МДФ ПАНЕЛИ: дешевле на ~80 тыс. ₽ (эконом ~110 тыс.), быстрее (без покраски), ровный цвет; боится воды и сильных ударов, во влажных зонах хуже дерева, выглядит «офиснее», сложнее точечный ремонт.
+Для посуточной: вагонка обычно даёт более дорогой визуал в объявлении; МДФ — разумная экономия, если бюджет жмёт. С/у в любом случае лучше плиткой (уже в смете).
+Пол — ламинат 33 кл. в обоих вариантах (~103 500 ₽).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5884,7 +6098,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Прихожая 2,80 м²</t>
         </is>
@@ -5932,7 +6146,7 @@
       <c r="C6" s="22" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Кухня-гостиная 18,82 м²</t>
         </is>
@@ -5993,7 +6207,7 @@
       <c r="C12" s="22" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Спальня 1 — 9,21 м²</t>
         </is>
@@ -6041,7 +6255,7 @@
       <c r="C17" s="22" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Спальня 2 — 9,21 м²</t>
         </is>
@@ -6089,7 +6303,7 @@
       <c r="C22" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>Санузел 3,32 м²</t>
         </is>
@@ -6165,7 +6379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6351,21 +6565,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1–3 дн: электрика черновая + вода/канализация + линии под конвекторы</t>
+          <t>1–3 дн: электрика черновая + вода/канализация + линии под конвекторы и улицу</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4–8 дн: обшивка перегородок/стен ГКЛ, потолки</t>
+          <t>4–10 дн: обрешётка + вагонка стены и потолки + покраска белая</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9–12 дн: шпаклёвка, откосы окон изнутри</t>
+          <t>11–12 дн: откосы окон, наличники, галтели</t>
         </is>
       </c>
     </row>
@@ -6379,14 +6593,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17–19 дн: покраска, ламинат, плинтуса</t>
+          <t>17–19 дн: ламинат, плинтуса</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20–22 дн: двери, чистовая электрика, конвекторы, сантехника</t>
+          <t>20–22 дн: двери, чистовая электрика, конвекторы, уличная подсветка, сантехника</t>
         </is>
       </c>
     </row>
